--- a/public/data/main-source-v3_operational_enhanced.xlsx
+++ b/public/data/main-source-v3_operational_enhanced.xlsx
@@ -436,13 +436,13 @@
     <t>John Carter</t>
   </si>
   <si>
-    <t>1240 W 6th St, Cleveland, OH 44113</t>
-  </si>
-  <si>
-    <t>206-667-3424</t>
-  </si>
-  <si>
-    <t>***-**-9443</t>
+    <t>220 Demo Street, Cleveland, OH 44113</t>
+  </si>
+  <si>
+    <t>206-555-0102</t>
+  </si>
+  <si>
+    <t>***-**-0123</t>
   </si>
   <si>
     <t>Huntington</t>
@@ -454,7 +454,7 @@
     <t>VALID</t>
   </si>
   <si>
-    <t>OH1668243</t>
+    <t>OH0000075</t>
   </si>
   <si>
     <t>Black</t>
@@ -475,10 +475,10 @@
     <t>Caucasian</t>
   </si>
   <si>
-    <t>jcarter@yahoo.com</t>
-  </si>
-  <si>
-    <t>1240 W 6th St</t>
+    <t>jcarter@example.com</t>
+  </si>
+  <si>
+    <t>220 Demo Street</t>
   </si>
   <si>
     <t>Cleveland</t>
@@ -574,7 +574,7 @@
     <t>CDL Holder</t>
   </si>
   <si>
-    <t>(614) 821-5212</t>
+    <t>(614) 555-0107</t>
   </si>
   <si>
     <t>OH-ME-970443</t>
@@ -625,58 +625,58 @@
     <t>Medical Certification</t>
   </si>
   <si>
-    <t>OH2933152</t>
-  </si>
-  <si>
-    <t>OH1668244</t>
+    <t>OH0000092</t>
+  </si>
+  <si>
+    <t>OH0000076</t>
   </si>
   <si>
     <t>MVR Background Report</t>
   </si>
   <si>
-    <t>OH6381314</t>
-  </si>
-  <si>
-    <t>OH1668245</t>
+    <t>OH0000111</t>
+  </si>
+  <si>
+    <t>OH0000077</t>
   </si>
   <si>
     <t>Driver Application</t>
   </si>
   <si>
-    <t>OH8275310</t>
-  </si>
-  <si>
-    <t>OH1668246</t>
+    <t>OH0000127</t>
+  </si>
+  <si>
+    <t>OH0000078</t>
   </si>
   <si>
     <t>Road Test Certificate</t>
   </si>
   <si>
-    <t>OH8643525</t>
-  </si>
-  <si>
-    <t>OH1668247</t>
+    <t>OH0000137</t>
+  </si>
+  <si>
+    <t>OH0000079</t>
   </si>
   <si>
     <t>Incident/Accident Report</t>
   </si>
   <si>
-    <t>OH8694835</t>
+    <t>OH0000138</t>
   </si>
   <si>
     <t>Load L-501: Seal mismatch detected. Pickup: SEAL-83921 Delivery: SEAL-83920.</t>
   </si>
   <si>
-    <t>OH1668248</t>
+    <t>OH0000080</t>
   </si>
   <si>
     <t>Direct Deposit Form</t>
   </si>
   <si>
-    <t>OH7359899</t>
-  </si>
-  <si>
-    <t>OH1668249</t>
+    <t>OH0000124</t>
+  </si>
+  <si>
+    <t>OH0000081</t>
   </si>
   <si>
     <t>DRV-002</t>
@@ -685,19 +685,19 @@
     <t>Maria Lopez</t>
   </si>
   <si>
-    <t>450 N Michigan Ave, Chicago, IL 60611</t>
-  </si>
-  <si>
-    <t>707-773-6386</t>
-  </si>
-  <si>
-    <t>***-**-3407</t>
+    <t>770 Demo Street, Chicago, IL 60611</t>
+  </si>
+  <si>
+    <t>707-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0105</t>
   </si>
   <si>
     <t>Chase</t>
   </si>
   <si>
-    <t>IL3091126</t>
+    <t>IL0000041</t>
   </si>
   <si>
     <t>Brown</t>
@@ -718,10 +718,10 @@
     <t>Hispanic</t>
   </si>
   <si>
-    <t>marialopez@aol.com</t>
-  </si>
-  <si>
-    <t>450 N Michigan Ave</t>
+    <t>marialopez@example.com</t>
+  </si>
+  <si>
+    <t>770 Demo Street</t>
   </si>
   <si>
     <t>Chicago</t>
@@ -763,7 +763,7 @@
     <t>Lopez</t>
   </si>
   <si>
-    <t>(312) 284-7914</t>
+    <t>(312) 555-0101</t>
   </si>
   <si>
     <t>IL-ME-425674</t>
@@ -784,43 +784,43 @@
     <t>555-555-5555</t>
   </si>
   <si>
-    <t>IL9530000</t>
-  </si>
-  <si>
-    <t>IL3091127</t>
-  </si>
-  <si>
-    <t>IL3900948</t>
-  </si>
-  <si>
-    <t>IL3091128</t>
-  </si>
-  <si>
-    <t>IL6663817</t>
-  </si>
-  <si>
-    <t>IL3091129</t>
-  </si>
-  <si>
-    <t>IL9293900</t>
-  </si>
-  <si>
-    <t>IL3091130</t>
-  </si>
-  <si>
-    <t>IL4346440</t>
+    <t>IL0000068</t>
+  </si>
+  <si>
+    <t>IL0000042</t>
+  </si>
+  <si>
+    <t>IL0000056</t>
+  </si>
+  <si>
+    <t>IL0000043</t>
+  </si>
+  <si>
+    <t>IL0000065</t>
+  </si>
+  <si>
+    <t>IL0000044</t>
+  </si>
+  <si>
+    <t>IL0000067</t>
+  </si>
+  <si>
+    <t>IL0000045</t>
+  </si>
+  <si>
+    <t>IL0000058</t>
   </si>
   <si>
     <t>No major incidents recorded in last 90 days.</t>
   </si>
   <si>
-    <t>IL3091131</t>
-  </si>
-  <si>
-    <t>IL4913140</t>
-  </si>
-  <si>
-    <t>IL3091132</t>
+    <t>IL0000046</t>
+  </si>
+  <si>
+    <t>IL0000061</t>
+  </si>
+  <si>
+    <t>IL0000047</t>
   </si>
   <si>
     <t>DRV-003</t>
@@ -829,16 +829,16 @@
     <t>Alex Kim</t>
   </si>
   <si>
-    <t>780 Peachtree St, Atlanta, GA 30308</t>
-  </si>
-  <si>
-    <t>675-486-1335</t>
-  </si>
-  <si>
-    <t>***-**-7047</t>
-  </si>
-  <si>
-    <t>GA7446431</t>
+    <t>960 Demo Street, Atlanta, GA 30308</t>
+  </si>
+  <si>
+    <t>675-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0116</t>
+  </si>
+  <si>
+    <t>GA0000013</t>
   </si>
   <si>
     <t>Blue</t>
@@ -853,10 +853,10 @@
     <t>Asian</t>
   </si>
   <si>
-    <t>alexkim@gmail.com</t>
-  </si>
-  <si>
-    <t>780 Peachtree St</t>
+    <t>alexkim@example.com</t>
+  </si>
+  <si>
+    <t>960 Demo Street</t>
   </si>
   <si>
     <t>Atlanta</t>
@@ -895,7 +895,7 @@
     <t>Kim</t>
   </si>
   <si>
-    <t>(404) 720-5860</t>
+    <t>(404) 555-0107</t>
   </si>
   <si>
     <t>GA-ME-142937</t>
@@ -904,40 +904,40 @@
     <t>Advanced Practice Nurse</t>
   </si>
   <si>
-    <t>GA3549920</t>
-  </si>
-  <si>
-    <t>GA7446432</t>
-  </si>
-  <si>
-    <t>GA5957495</t>
-  </si>
-  <si>
-    <t>GA7446433</t>
-  </si>
-  <si>
-    <t>GA3499514</t>
-  </si>
-  <si>
-    <t>GA7446434</t>
-  </si>
-  <si>
-    <t>GA3381500</t>
-  </si>
-  <si>
-    <t>GA7446435</t>
-  </si>
-  <si>
-    <t>GA8768417</t>
-  </si>
-  <si>
-    <t>GA7446436</t>
-  </si>
-  <si>
-    <t>GA1828575</t>
-  </si>
-  <si>
-    <t>GA7446437</t>
+    <t>GA0000006</t>
+  </si>
+  <si>
+    <t>GA0000014</t>
+  </si>
+  <si>
+    <t>GA0000011</t>
+  </si>
+  <si>
+    <t>GA0000015</t>
+  </si>
+  <si>
+    <t>GA0000005</t>
+  </si>
+  <si>
+    <t>GA0000016</t>
+  </si>
+  <si>
+    <t>GA0000004</t>
+  </si>
+  <si>
+    <t>GA0000017</t>
+  </si>
+  <si>
+    <t>GA0000027</t>
+  </si>
+  <si>
+    <t>GA0000018</t>
+  </si>
+  <si>
+    <t>GA0000002</t>
+  </si>
+  <si>
+    <t>GA0000019</t>
   </si>
   <si>
     <t>DRV-004</t>
@@ -946,16 +946,16 @@
     <t>Priya Patel</t>
   </si>
   <si>
-    <t>2200 Superior Ave, Cleveland, OH 44114</t>
-  </si>
-  <si>
-    <t>359-469-5960</t>
-  </si>
-  <si>
-    <t>***-**-8257</t>
-  </si>
-  <si>
-    <t>OH8493496</t>
+    <t>520 Demo Street, Cleveland, OH 44114</t>
+  </si>
+  <si>
+    <t>359-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0119</t>
+  </si>
+  <si>
+    <t>OH0000130</t>
   </si>
   <si>
     <t>5'-7"</t>
@@ -967,10 +967,10 @@
     <t>South Asian</t>
   </si>
   <si>
-    <t>priyapatel@yahoo.com</t>
-  </si>
-  <si>
-    <t>2200 Superior Ave</t>
+    <t>priyapatel@example.com</t>
+  </si>
+  <si>
+    <t>520 Demo Street</t>
   </si>
   <si>
     <t>Automatic transmission only</t>
@@ -1000,52 +1000,52 @@
     <t>Patel</t>
   </si>
   <si>
-    <t>(614) 897-8705</t>
+    <t>(614) 555-0111</t>
   </si>
   <si>
     <t>OH-ME-293591</t>
   </si>
   <si>
-    <t>OH4694295</t>
-  </si>
-  <si>
-    <t>OH8493497</t>
-  </si>
-  <si>
-    <t>OH7280038</t>
-  </si>
-  <si>
-    <t>OH8493498</t>
+    <t>OH0000099</t>
+  </si>
+  <si>
+    <t>OH0000131</t>
+  </si>
+  <si>
+    <t>OH0000123</t>
+  </si>
+  <si>
+    <t>OH0000132</t>
   </si>
   <si>
     <t>summary</t>
   </si>
   <si>
-    <t>OH9775880</t>
-  </si>
-  <si>
-    <t>OH8493499</t>
-  </si>
-  <si>
-    <t>OH1046362</t>
-  </si>
-  <si>
-    <t>OH8493500</t>
-  </si>
-  <si>
-    <t>OH1138650</t>
+    <t>OH0000149</t>
+  </si>
+  <si>
+    <t>OH0000133</t>
+  </si>
+  <si>
+    <t>OH0000072</t>
+  </si>
+  <si>
+    <t>OH0000134</t>
+  </si>
+  <si>
+    <t>OH0000074</t>
   </si>
   <si>
     <t>Load L-504: Seal mismatch detected. Pickup: SEAL-61044 Delivery: SEAL-61043.</t>
   </si>
   <si>
-    <t>OH8493501</t>
-  </si>
-  <si>
-    <t>OH4059570</t>
-  </si>
-  <si>
-    <t>OH8493502</t>
+    <t>OH0000135</t>
+  </si>
+  <si>
+    <t>OH0000095</t>
+  </si>
+  <si>
+    <t>OH0000136</t>
   </si>
   <si>
     <t>DRV-005</t>
@@ -1054,25 +1054,25 @@
     <t>Kenji Tanaka</t>
   </si>
   <si>
-    <t>115 E Broad St, Columbus, OH 43215</t>
-  </si>
-  <si>
-    <t>871-429-6220</t>
-  </si>
-  <si>
-    <t>***-**-1789</t>
-  </si>
-  <si>
-    <t>OH2779041</t>
+    <t>150 Demo Street, Columbus, OH 43215</t>
+  </si>
+  <si>
+    <t>871-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0102</t>
+  </si>
+  <si>
+    <t>OH0000084</t>
   </si>
   <si>
     <t>DRV-005.png</t>
   </si>
   <si>
-    <t>ktanaka@yahoo.com</t>
-  </si>
-  <si>
-    <t>115 E Broad St</t>
+    <t>ktanaka@example.com</t>
+  </si>
+  <si>
+    <t>150 Demo Street</t>
   </si>
   <si>
     <t>Columbus</t>
@@ -1102,46 +1102,46 @@
     <t>Tanaka</t>
   </si>
   <si>
-    <t>(614) 806-7535</t>
+    <t>(614) 555-0106</t>
   </si>
   <si>
     <t>OH-ME-401933</t>
   </si>
   <si>
-    <t>OH3434069</t>
-  </si>
-  <si>
-    <t>OH2779042</t>
-  </si>
-  <si>
-    <t>OH6720716</t>
-  </si>
-  <si>
-    <t>OH2779043</t>
-  </si>
-  <si>
-    <t>OH5640312</t>
-  </si>
-  <si>
-    <t>OH2779044</t>
-  </si>
-  <si>
-    <t>OH7627072</t>
-  </si>
-  <si>
-    <t>OH2779045</t>
-  </si>
-  <si>
-    <t>OH1919210</t>
-  </si>
-  <si>
-    <t>OH2779046</t>
-  </si>
-  <si>
-    <t>OH7765263</t>
-  </si>
-  <si>
-    <t>OH2779047</t>
+    <t>OH0000093</t>
+  </si>
+  <si>
+    <t>OH0000085</t>
+  </si>
+  <si>
+    <t>OH0000119</t>
+  </si>
+  <si>
+    <t>OH0000086</t>
+  </si>
+  <si>
+    <t>OH0000102</t>
+  </si>
+  <si>
+    <t>OH0000087</t>
+  </si>
+  <si>
+    <t>OH0000125</t>
+  </si>
+  <si>
+    <t>OH0000088</t>
+  </si>
+  <si>
+    <t>OH0000082</t>
+  </si>
+  <si>
+    <t>OH0000089</t>
+  </si>
+  <si>
+    <t>OH0000126</t>
+  </si>
+  <si>
+    <t>OH0000090</t>
   </si>
   <si>
     <t>DRV-006</t>
@@ -1150,16 +1150,16 @@
     <t>Marcus Chen</t>
   </si>
   <si>
-    <t>500 Pacific Ave, Dallas, TX 75202</t>
-  </si>
-  <si>
-    <t>283-876-4322</t>
-  </si>
-  <si>
-    <t>***-**-1521</t>
-  </si>
-  <si>
-    <t>TX3261112</t>
+    <t>810 Demo Street, Dallas, TX 75202</t>
+  </si>
+  <si>
+    <t>283-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0101</t>
+  </si>
+  <si>
+    <t>TX0000158</t>
   </si>
   <si>
     <t>Bald</t>
@@ -1171,10 +1171,10 @@
     <t>DRV-006.png</t>
   </si>
   <si>
-    <t>mchen@hotmail.com</t>
-  </si>
-  <si>
-    <t>500 Pacific Ave</t>
+    <t>mchen@example.com</t>
+  </si>
+  <si>
+    <t>810 Demo Street</t>
   </si>
   <si>
     <t>Dallas</t>
@@ -1213,7 +1213,7 @@
     <t>Chen</t>
   </si>
   <si>
-    <t>(512) 621-2178</t>
+    <t>(512) 555-0100</t>
   </si>
   <si>
     <t>TX-ME-991196</t>
@@ -1222,40 +1222,40 @@
     <t>Physician Assistant</t>
   </si>
   <si>
-    <t>TX3531641</t>
-  </si>
-  <si>
-    <t>TX3261113</t>
-  </si>
-  <si>
-    <t>TX2647879</t>
-  </si>
-  <si>
-    <t>TX3261114</t>
-  </si>
-  <si>
-    <t>TX3779357</t>
-  </si>
-  <si>
-    <t>TX3261115</t>
-  </si>
-  <si>
-    <t>TX3175879</t>
-  </si>
-  <si>
-    <t>TX3261116</t>
-  </si>
-  <si>
-    <t>TX8659153</t>
-  </si>
-  <si>
-    <t>TX3261117</t>
-  </si>
-  <si>
-    <t>TX3212501</t>
-  </si>
-  <si>
-    <t>TX3261118</t>
+    <t>TX0000165</t>
+  </si>
+  <si>
+    <t>TX0000159</t>
+  </si>
+  <si>
+    <t>TX0000155</t>
+  </si>
+  <si>
+    <t>TX0000160</t>
+  </si>
+  <si>
+    <t>TX0000166</t>
+  </si>
+  <si>
+    <t>TX0000161</t>
+  </si>
+  <si>
+    <t>TX0000156</t>
+  </si>
+  <si>
+    <t>TX0000162</t>
+  </si>
+  <si>
+    <t>TX0000167</t>
+  </si>
+  <si>
+    <t>TX0000163</t>
+  </si>
+  <si>
+    <t>TX0000157</t>
+  </si>
+  <si>
+    <t>TX0000164</t>
   </si>
   <si>
     <t>DRV-007</t>
@@ -1264,19 +1264,19 @@
     <t>Sofia Gomez</t>
   </si>
   <si>
-    <t>815 Prospect Ave, Cleveland, OH 44115</t>
-  </si>
-  <si>
-    <t>896-828-7164</t>
-  </si>
-  <si>
-    <t>***-**-4815</t>
+    <t>1020 Demo Street, Cleveland, OH 44115</t>
+  </si>
+  <si>
+    <t>896-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0109</t>
   </si>
   <si>
     <t>Bank of America</t>
   </si>
   <si>
-    <t>OH6635833</t>
+    <t>OH0000112</t>
   </si>
   <si>
     <t>Blonde</t>
@@ -1288,10 +1288,10 @@
     <t>DRV-007.png</t>
   </si>
   <si>
-    <t>sofiagomez@yahoo.com</t>
-  </si>
-  <si>
-    <t>815 Prospect Ave</t>
+    <t>sofiagomez@example.com</t>
+  </si>
+  <si>
+    <t>1020 Demo Street</t>
   </si>
   <si>
     <t>MC-0071214</t>
@@ -1318,7 +1318,7 @@
     <t>Gomez</t>
   </si>
   <si>
-    <t>(614) 574-7480</t>
+    <t>(614) 555-0105</t>
   </si>
   <si>
     <t>OH-ME-801071</t>
@@ -1327,43 +1327,43 @@
     <t>DO</t>
   </si>
   <si>
-    <t>OH6094308</t>
-  </si>
-  <si>
-    <t>OH6635834</t>
-  </si>
-  <si>
-    <t>OH5247055</t>
-  </si>
-  <si>
-    <t>OH6635835</t>
-  </si>
-  <si>
-    <t>OH8453480</t>
-  </si>
-  <si>
-    <t>OH6635836</t>
-  </si>
-  <si>
-    <t>OH6843221</t>
-  </si>
-  <si>
-    <t>OH6635837</t>
-  </si>
-  <si>
-    <t>OH6877493</t>
+    <t>OH0000103</t>
+  </si>
+  <si>
+    <t>OH0000113</t>
+  </si>
+  <si>
+    <t>OH0000101</t>
+  </si>
+  <si>
+    <t>OH0000114</t>
+  </si>
+  <si>
+    <t>OH0000129</t>
+  </si>
+  <si>
+    <t>OH0000115</t>
+  </si>
+  <si>
+    <t>OH0000120</t>
+  </si>
+  <si>
+    <t>OH0000116</t>
+  </si>
+  <si>
+    <t>OH0000121</t>
   </si>
   <si>
     <t>Load L-507: Seal mismatch detected. Pickup: SEAL-73005 Delivery: SEAL-73099.</t>
   </si>
   <si>
-    <t>OH6635838</t>
-  </si>
-  <si>
-    <t>OH1110710</t>
-  </si>
-  <si>
-    <t>OH6635839</t>
+    <t>OH0000117</t>
+  </si>
+  <si>
+    <t>OH0000073</t>
+  </si>
+  <si>
+    <t>OH0000118</t>
   </si>
   <si>
     <t>DRV-008</t>
@@ -1372,28 +1372,28 @@
     <t>Liam Smith</t>
   </si>
   <si>
-    <t>240 Madison Ave, Toledo, OH 43604</t>
-  </si>
-  <si>
-    <t>820-223-4829</t>
-  </si>
-  <si>
-    <t>***-**-4800</t>
+    <t>530 Demo Street, Toledo, OH 43604</t>
+  </si>
+  <si>
+    <t>820-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0108</t>
   </si>
   <si>
     <t>PNC</t>
   </si>
   <si>
-    <t>OH9450480</t>
+    <t>OH0000141</t>
   </si>
   <si>
     <t>DRV-008.png</t>
   </si>
   <si>
-    <t>liamsmith@gmail.com</t>
-  </si>
-  <si>
-    <t>240 Madison Ave</t>
+    <t>liamsmith@example.com</t>
+  </si>
+  <si>
+    <t>530 Demo Street</t>
   </si>
   <si>
     <t>Toledo</t>
@@ -1429,7 +1429,7 @@
     <t>Smith</t>
   </si>
   <si>
-    <t>(614) 937-6329</t>
+    <t>(614) 555-0114</t>
   </si>
   <si>
     <t>OH-ME-134036</t>
@@ -1438,40 +1438,40 @@
     <t>Federal Motor Carrier Safety Regulations with applicable State variances</t>
   </si>
   <si>
-    <t>OH8889985</t>
-  </si>
-  <si>
-    <t>OH9450481</t>
-  </si>
-  <si>
-    <t>OH2899009</t>
-  </si>
-  <si>
-    <t>OH9450482</t>
-  </si>
-  <si>
-    <t>OH8294998</t>
-  </si>
-  <si>
-    <t>OH9450483</t>
-  </si>
-  <si>
-    <t>OH3539286</t>
-  </si>
-  <si>
-    <t>OH9450484</t>
-  </si>
-  <si>
-    <t>OH4520738</t>
-  </si>
-  <si>
-    <t>OH9450485</t>
-  </si>
-  <si>
-    <t>OH9851872</t>
-  </si>
-  <si>
-    <t>OH9450486</t>
+    <t>OH0000139</t>
+  </si>
+  <si>
+    <t>OH0000142</t>
+  </si>
+  <si>
+    <t>OH0000091</t>
+  </si>
+  <si>
+    <t>OH0000143</t>
+  </si>
+  <si>
+    <t>OH0000128</t>
+  </si>
+  <si>
+    <t>OH0000144</t>
+  </si>
+  <si>
+    <t>OH0000094</t>
+  </si>
+  <si>
+    <t>OH0000145</t>
+  </si>
+  <si>
+    <t>OH0000098</t>
+  </si>
+  <si>
+    <t>OH0000146</t>
+  </si>
+  <si>
+    <t>OH0000150</t>
+  </si>
+  <si>
+    <t>OH0000147</t>
   </si>
   <si>
     <t>DRV-009</t>
@@ -1480,25 +1480,25 @@
     <t>Emma Brown</t>
   </si>
   <si>
-    <t>330 Civic Center Dr, Columbus, OH 43215</t>
-  </si>
-  <si>
-    <t>206-700-7666</t>
-  </si>
-  <si>
-    <t>***-**-9930</t>
-  </si>
-  <si>
-    <t>OH6116714</t>
+    <t>630 Demo Street, Columbus, OH 43215</t>
+  </si>
+  <si>
+    <t>206-555-0103</t>
+  </si>
+  <si>
+    <t>***-**-0124</t>
+  </si>
+  <si>
+    <t>OH0000104</t>
   </si>
   <si>
     <t>DRV-009.png</t>
   </si>
   <si>
-    <t>emmabrown@yahoo.com</t>
-  </si>
-  <si>
-    <t>330 Civic Center Dr</t>
+    <t>emmabrown@example.com</t>
+  </si>
+  <si>
+    <t>630 Demo Street</t>
   </si>
   <si>
     <t>Class B</t>
@@ -1528,46 +1528,46 @@
     <t>Emma</t>
   </si>
   <si>
-    <t>(614) 935-8132</t>
+    <t>(614) 555-0113</t>
   </si>
   <si>
     <t>OH-ME-556547</t>
   </si>
   <si>
-    <t>OH2742151</t>
-  </si>
-  <si>
-    <t>OH6116715</t>
-  </si>
-  <si>
-    <t>OH5031927</t>
-  </si>
-  <si>
-    <t>OH6116716</t>
-  </si>
-  <si>
-    <t>OH9570143</t>
-  </si>
-  <si>
-    <t>OH6116717</t>
-  </si>
-  <si>
-    <t>OH7265424</t>
-  </si>
-  <si>
-    <t>OH6116718</t>
-  </si>
-  <si>
-    <t>OH4179820</t>
-  </si>
-  <si>
-    <t>OH6116719</t>
-  </si>
-  <si>
-    <t>OH9306784</t>
-  </si>
-  <si>
-    <t>OH6116720</t>
+    <t>OH0000083</t>
+  </si>
+  <si>
+    <t>OH0000105</t>
+  </si>
+  <si>
+    <t>OH0000100</t>
+  </si>
+  <si>
+    <t>OH0000106</t>
+  </si>
+  <si>
+    <t>OH0000148</t>
+  </si>
+  <si>
+    <t>OH0000107</t>
+  </si>
+  <si>
+    <t>OH0000122</t>
+  </si>
+  <si>
+    <t>OH0000108</t>
+  </si>
+  <si>
+    <t>OH0000096</t>
+  </si>
+  <si>
+    <t>OH0000109</t>
+  </si>
+  <si>
+    <t>OH0000140</t>
+  </si>
+  <si>
+    <t>OH0000110</t>
   </si>
   <si>
     <t>DRV-010</t>
@@ -1576,16 +1576,16 @@
     <t>Noah Wilson</t>
   </si>
   <si>
-    <t>110 W Adams St, Chicago, IL 60603</t>
-  </si>
-  <si>
-    <t>582-987-2387</t>
-  </si>
-  <si>
-    <t>***-**-5590</t>
-  </si>
-  <si>
-    <t>IL3858215</t>
+    <t>130 Demo Street, Chicago, IL 60603</t>
+  </si>
+  <si>
+    <t>582-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0112</t>
+  </si>
+  <si>
+    <t>IL0000049</t>
   </si>
   <si>
     <t>6'-3"</t>
@@ -1594,10 +1594,10 @@
     <t>DRV-010.png</t>
   </si>
   <si>
-    <t>nwilson@gmail.com</t>
-  </si>
-  <si>
-    <t>110 W Adams St</t>
+    <t>nwilson@example.com</t>
+  </si>
+  <si>
+    <t>130 Demo Street</t>
   </si>
   <si>
     <t>MC-0100911</t>
@@ -1618,46 +1618,46 @@
     <t>Wilson</t>
   </si>
   <si>
-    <t>(312) 807-8788</t>
+    <t>(312) 555-0109</t>
   </si>
   <si>
     <t>IL-ME-366300</t>
   </si>
   <si>
-    <t>IL2016981</t>
-  </si>
-  <si>
-    <t>IL3858216</t>
-  </si>
-  <si>
-    <t>IL4814730</t>
-  </si>
-  <si>
-    <t>IL3858217</t>
-  </si>
-  <si>
-    <t>IL4355788</t>
-  </si>
-  <si>
-    <t>IL3858218</t>
-  </si>
-  <si>
-    <t>IL6567205</t>
-  </si>
-  <si>
-    <t>IL3858219</t>
-  </si>
-  <si>
-    <t>IL6135045</t>
-  </si>
-  <si>
-    <t>IL3858220</t>
-  </si>
-  <si>
-    <t>IL2535912</t>
-  </si>
-  <si>
-    <t>IL3858221</t>
+    <t>IL0000037</t>
+  </si>
+  <si>
+    <t>IL0000050</t>
+  </si>
+  <si>
+    <t>IL0000060</t>
+  </si>
+  <si>
+    <t>IL0000051</t>
+  </si>
+  <si>
+    <t>IL0000059</t>
+  </si>
+  <si>
+    <t>IL0000052</t>
+  </si>
+  <si>
+    <t>IL0000064</t>
+  </si>
+  <si>
+    <t>IL0000053</t>
+  </si>
+  <si>
+    <t>IL0000063</t>
+  </si>
+  <si>
+    <t>IL0000054</t>
+  </si>
+  <si>
+    <t>IL0000038</t>
+  </si>
+  <si>
+    <t>IL0000055</t>
   </si>
   <si>
     <t>DRV-011</t>
@@ -1666,16 +1666,16 @@
     <t>Olivia Lee</t>
   </si>
   <si>
-    <t>600 Peachtree St, Atlanta, GA 30308</t>
-  </si>
-  <si>
-    <t>337-857-3607</t>
-  </si>
-  <si>
-    <t>***-**-5273</t>
-  </si>
-  <si>
-    <t>GA8190601</t>
+    <t>900 Demo Street, Atlanta, GA 30308</t>
+  </si>
+  <si>
+    <t>337-555-0100</t>
+  </si>
+  <si>
+    <t>***-**-0111</t>
+  </si>
+  <si>
+    <t>GA0000020</t>
   </si>
   <si>
     <t>5'-5"</t>
@@ -1684,10 +1684,10 @@
     <t>DRV-011.png</t>
   </si>
   <si>
-    <t>olee@hotmail.com</t>
-  </si>
-  <si>
-    <t>600 Peachtree St</t>
+    <t>olee@example.com</t>
+  </si>
+  <si>
+    <t>900 Demo Street</t>
   </si>
   <si>
     <t>MC-0110314</t>
@@ -1708,46 +1708,46 @@
     <t>Lee</t>
   </si>
   <si>
-    <t>(404) 231-4428</t>
+    <t>(404) 555-0100</t>
   </si>
   <si>
     <t>GA-ME-601747</t>
   </si>
   <si>
-    <t>GA4750278</t>
-  </si>
-  <si>
-    <t>GA8190602</t>
-  </si>
-  <si>
-    <t>GA5818610</t>
-  </si>
-  <si>
-    <t>GA8190603</t>
-  </si>
-  <si>
-    <t>GA5852321</t>
-  </si>
-  <si>
-    <t>GA8190604</t>
-  </si>
-  <si>
-    <t>GA6447082</t>
-  </si>
-  <si>
-    <t>GA8190605</t>
-  </si>
-  <si>
-    <t>GA5384195</t>
-  </si>
-  <si>
-    <t>GA8190606</t>
-  </si>
-  <si>
-    <t>GA1861689</t>
-  </si>
-  <si>
-    <t>GA8190607</t>
+    <t>GA0000007</t>
+  </si>
+  <si>
+    <t>GA0000021</t>
+  </si>
+  <si>
+    <t>GA0000009</t>
+  </si>
+  <si>
+    <t>GA0000022</t>
+  </si>
+  <si>
+    <t>GA0000010</t>
+  </si>
+  <si>
+    <t>GA0000023</t>
+  </si>
+  <si>
+    <t>GA0000012</t>
+  </si>
+  <si>
+    <t>GA0000024</t>
+  </si>
+  <si>
+    <t>GA0000008</t>
+  </si>
+  <si>
+    <t>GA0000025</t>
+  </si>
+  <si>
+    <t>GA0000003</t>
+  </si>
+  <si>
+    <t>GA0000026</t>
   </si>
   <si>
     <t>DRV-012</t>
@@ -1756,28 +1756,28 @@
     <t>Robert Johnson</t>
   </si>
   <si>
-    <t>618 S Michigan Ave, Chicago, IL 60605</t>
-  </si>
-  <si>
-    <t>618-667-2121</t>
-  </si>
-  <si>
-    <t>***-**-5664</t>
+    <t>920 Demo Street, Chicago, IL 60605</t>
+  </si>
+  <si>
+    <t>618-555-0101</t>
+  </si>
+  <si>
+    <t>***-**-0114</t>
   </si>
   <si>
     <t>Wells Fargo</t>
   </si>
   <si>
-    <t>IL1895570</t>
+    <t>IL0000030</t>
   </si>
   <si>
     <t>DRV-012.png</t>
   </si>
   <si>
-    <t>robertjohnson@hotmail.com</t>
-  </si>
-  <si>
-    <t>618 S Michigan Ave</t>
+    <t>robertjohnson@example.com</t>
+  </si>
+  <si>
+    <t>920 Demo Street</t>
   </si>
   <si>
     <t>MC-0120411</t>
@@ -1798,118 +1798,118 @@
     <t>Johnson</t>
   </si>
   <si>
-    <t>(312) 300-1431</t>
+    <t>(312) 555-0103</t>
   </si>
   <si>
     <t>IL-ME-120233</t>
   </si>
   <si>
-    <t>IL5451183</t>
-  </si>
-  <si>
-    <t>IL1895571</t>
-  </si>
-  <si>
-    <t>IL2852329</t>
-  </si>
-  <si>
-    <t>IL1895572</t>
-  </si>
-  <si>
-    <t>IL4305571</t>
-  </si>
-  <si>
-    <t>IL1895573</t>
-  </si>
-  <si>
-    <t>IL8325086</t>
-  </si>
-  <si>
-    <t>IL1895574</t>
-  </si>
-  <si>
-    <t>IL3423206</t>
+    <t>IL0000062</t>
+  </si>
+  <si>
+    <t>IL0000031</t>
+  </si>
+  <si>
+    <t>IL0000040</t>
+  </si>
+  <si>
+    <t>IL0000032</t>
+  </si>
+  <si>
+    <t>IL0000057</t>
+  </si>
+  <si>
+    <t>IL0000033</t>
+  </si>
+  <si>
+    <t>IL0000066</t>
+  </si>
+  <si>
+    <t>IL0000034</t>
+  </si>
+  <si>
+    <t>IL0000048</t>
   </si>
   <si>
     <t>Load L-512: Seal broken upon arrival. Theft suspected.</t>
   </si>
   <si>
-    <t>IL1895575</t>
-  </si>
-  <si>
-    <t>IL2655126</t>
-  </si>
-  <si>
-    <t>IL1895576</t>
-  </si>
-  <si>
-    <t>DRV-001    322-40-9443</t>
+    <t>IL0000035</t>
+  </si>
+  <si>
+    <t>IL0000039</t>
+  </si>
+  <si>
+    <t>IL0000036</t>
+  </si>
+  <si>
+    <t>DRV-001    900-00-0123</t>
   </si>
   <si>
     <t>John T. Carter</t>
   </si>
   <si>
-    <t>DRV-002    164-67-3407</t>
+    <t>DRV-002    900-00-0105</t>
   </si>
   <si>
     <t>Maria E. Lopez</t>
   </si>
   <si>
-    <t>DRV-003    997-32-7047</t>
+    <t>DRV-003    900-00-0116</t>
   </si>
   <si>
     <t>Alex J. Kim</t>
   </si>
   <si>
-    <t>DRV-004    136-33-8257</t>
+    <t>DRV-004    900-00-0119</t>
   </si>
   <si>
     <t>Priya A. Patel</t>
   </si>
   <si>
-    <t>DRV-005    438-27-1789</t>
+    <t>DRV-005    900-00-0102</t>
   </si>
   <si>
     <t>Kenji H. Tanaka</t>
   </si>
   <si>
-    <t>DRV-006    121-25-1521</t>
+    <t>DRV-006    900-00-0101</t>
   </si>
   <si>
     <t>Marcus W. Chen</t>
   </si>
   <si>
-    <t>DRV-007    560-64-4815</t>
+    <t>DRV-007    900-00-0109</t>
   </si>
   <si>
     <t>Sofia I. Gomez</t>
   </si>
   <si>
-    <t>DRV-008    441-80-4800</t>
+    <t>DRV-008    900-00-0108</t>
   </si>
   <si>
     <t>Liam P. Smith</t>
   </si>
   <si>
-    <t>DRV-009    876-90-9930</t>
+    <t>DRV-009    900-00-0124</t>
   </si>
   <si>
     <t>Emma C. Brown</t>
   </si>
   <si>
-    <t>DRV-010    609-69-5590</t>
+    <t>DRV-010    900-00-0112</t>
   </si>
   <si>
     <t>Noah R. Wilson</t>
   </si>
   <si>
-    <t>DRV-011    389-76-5273</t>
+    <t>DRV-011    900-00-0111</t>
   </si>
   <si>
     <t>Olivia M. Lee</t>
   </si>
   <si>
-    <t>DRV-012    815-21-5664</t>
+    <t>DRV-012    900-00-0114</t>
   </si>
   <si>
     <t>Robert D. Johnson</t>
@@ -7603,10 +7603,10 @@
         <v>137</v>
       </c>
       <c r="G2">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H2">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I2" t="s">
         <v>138</v>
@@ -7642,7 +7642,7 @@
         <v>144</v>
       </c>
       <c r="U2" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V2" t="s">
         <v>145</v>
@@ -7965,10 +7965,10 @@
         <v>137</v>
       </c>
       <c r="G3">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H3">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I3" t="s">
         <v>196</v>
@@ -8004,7 +8004,7 @@
         <v>144</v>
       </c>
       <c r="U3" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V3" t="s">
         <v>145</v>
@@ -8327,10 +8327,10 @@
         <v>137</v>
       </c>
       <c r="G4">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H4">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I4" t="s">
         <v>199</v>
@@ -8366,7 +8366,7 @@
         <v>144</v>
       </c>
       <c r="U4" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V4" t="s">
         <v>145</v>
@@ -8689,10 +8689,10 @@
         <v>137</v>
       </c>
       <c r="G5">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H5">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I5" t="s">
         <v>202</v>
@@ -8728,7 +8728,7 @@
         <v>144</v>
       </c>
       <c r="U5" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V5" t="s">
         <v>145</v>
@@ -9051,10 +9051,10 @@
         <v>137</v>
       </c>
       <c r="G6">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H6">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I6" t="s">
         <v>205</v>
@@ -9090,7 +9090,7 @@
         <v>144</v>
       </c>
       <c r="U6" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V6" t="s">
         <v>145</v>
@@ -9413,10 +9413,10 @@
         <v>137</v>
       </c>
       <c r="G7">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H7">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I7" t="s">
         <v>208</v>
@@ -9455,7 +9455,7 @@
         <v>144</v>
       </c>
       <c r="U7" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V7" t="s">
         <v>145</v>
@@ -9778,10 +9778,10 @@
         <v>137</v>
       </c>
       <c r="G8">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H8">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I8" t="s">
         <v>212</v>
@@ -9817,7 +9817,7 @@
         <v>144</v>
       </c>
       <c r="U8" s="1">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V8" t="s">
         <v>145</v>
@@ -10140,10 +10140,10 @@
         <v>220</v>
       </c>
       <c r="G9">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H9">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I9" t="s">
         <v>138</v>
@@ -10179,7 +10179,7 @@
         <v>225</v>
       </c>
       <c r="U9" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V9" t="s">
         <v>226</v>
@@ -10514,10 +10514,10 @@
         <v>220</v>
       </c>
       <c r="G10">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H10">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I10" t="s">
         <v>196</v>
@@ -10553,7 +10553,7 @@
         <v>225</v>
       </c>
       <c r="U10" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V10" t="s">
         <v>226</v>
@@ -10888,10 +10888,10 @@
         <v>220</v>
       </c>
       <c r="G11">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H11">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I11" t="s">
         <v>199</v>
@@ -10927,7 +10927,7 @@
         <v>225</v>
       </c>
       <c r="U11" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V11" t="s">
         <v>226</v>
@@ -11262,10 +11262,10 @@
         <v>220</v>
       </c>
       <c r="G12">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H12">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I12" t="s">
         <v>202</v>
@@ -11301,7 +11301,7 @@
         <v>225</v>
       </c>
       <c r="U12" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V12" t="s">
         <v>226</v>
@@ -11636,10 +11636,10 @@
         <v>220</v>
       </c>
       <c r="G13">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H13">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I13" t="s">
         <v>205</v>
@@ -11675,7 +11675,7 @@
         <v>225</v>
       </c>
       <c r="U13" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V13" t="s">
         <v>226</v>
@@ -12010,10 +12010,10 @@
         <v>220</v>
       </c>
       <c r="G14">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H14">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I14" t="s">
         <v>208</v>
@@ -12052,7 +12052,7 @@
         <v>225</v>
       </c>
       <c r="U14" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V14" t="s">
         <v>226</v>
@@ -12387,10 +12387,10 @@
         <v>220</v>
       </c>
       <c r="G15">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H15">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I15" t="s">
         <v>212</v>
@@ -12426,7 +12426,7 @@
         <v>225</v>
       </c>
       <c r="U15" s="1">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V15" t="s">
         <v>226</v>
@@ -12761,10 +12761,10 @@
         <v>220</v>
       </c>
       <c r="G16">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H16">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I16" t="s">
         <v>138</v>
@@ -12800,7 +12800,7 @@
         <v>144</v>
       </c>
       <c r="U16" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V16" t="s">
         <v>271</v>
@@ -13126,10 +13126,10 @@
         <v>220</v>
       </c>
       <c r="G17">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H17">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I17" t="s">
         <v>196</v>
@@ -13165,7 +13165,7 @@
         <v>144</v>
       </c>
       <c r="U17" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V17" t="s">
         <v>271</v>
@@ -13491,10 +13491,10 @@
         <v>220</v>
       </c>
       <c r="G18">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H18">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I18" t="s">
         <v>199</v>
@@ -13530,7 +13530,7 @@
         <v>144</v>
       </c>
       <c r="U18" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V18" t="s">
         <v>271</v>
@@ -13856,10 +13856,10 @@
         <v>220</v>
       </c>
       <c r="G19">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H19">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I19" t="s">
         <v>202</v>
@@ -13895,7 +13895,7 @@
         <v>144</v>
       </c>
       <c r="U19" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V19" t="s">
         <v>271</v>
@@ -14221,10 +14221,10 @@
         <v>220</v>
       </c>
       <c r="G20">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H20">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I20" t="s">
         <v>205</v>
@@ -14260,7 +14260,7 @@
         <v>144</v>
       </c>
       <c r="U20" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V20" t="s">
         <v>271</v>
@@ -14586,10 +14586,10 @@
         <v>220</v>
       </c>
       <c r="G21">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H21">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I21" t="s">
         <v>208</v>
@@ -14628,7 +14628,7 @@
         <v>144</v>
       </c>
       <c r="U21" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V21" t="s">
         <v>271</v>
@@ -14954,10 +14954,10 @@
         <v>220</v>
       </c>
       <c r="G22">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H22">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I22" t="s">
         <v>212</v>
@@ -14993,7 +14993,7 @@
         <v>144</v>
       </c>
       <c r="U22" s="1">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V22" t="s">
         <v>271</v>
@@ -15319,10 +15319,10 @@
         <v>220</v>
       </c>
       <c r="G23">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H23">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I23" t="s">
         <v>138</v>
@@ -15358,7 +15358,7 @@
         <v>225</v>
       </c>
       <c r="U23" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V23" t="s">
         <v>309</v>
@@ -15690,10 +15690,10 @@
         <v>220</v>
       </c>
       <c r="G24">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H24">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I24" t="s">
         <v>196</v>
@@ -15729,7 +15729,7 @@
         <v>225</v>
       </c>
       <c r="U24" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V24" t="s">
         <v>309</v>
@@ -16061,10 +16061,10 @@
         <v>220</v>
       </c>
       <c r="G25">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H25">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I25" t="s">
         <v>199</v>
@@ -16100,7 +16100,7 @@
         <v>225</v>
       </c>
       <c r="U25" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V25" t="s">
         <v>309</v>
@@ -16432,10 +16432,10 @@
         <v>220</v>
       </c>
       <c r="G26">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H26">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I26" t="s">
         <v>328</v>
@@ -16471,7 +16471,7 @@
         <v>225</v>
       </c>
       <c r="U26" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V26" t="s">
         <v>309</v>
@@ -16803,10 +16803,10 @@
         <v>220</v>
       </c>
       <c r="G27">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H27">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I27" t="s">
         <v>205</v>
@@ -16842,7 +16842,7 @@
         <v>225</v>
       </c>
       <c r="U27" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V27" t="s">
         <v>309</v>
@@ -17174,10 +17174,10 @@
         <v>220</v>
       </c>
       <c r="G28">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H28">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I28" t="s">
         <v>208</v>
@@ -17216,7 +17216,7 @@
         <v>225</v>
       </c>
       <c r="U28" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V28" t="s">
         <v>309</v>
@@ -17548,10 +17548,10 @@
         <v>220</v>
       </c>
       <c r="G29">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H29">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I29" t="s">
         <v>212</v>
@@ -17587,7 +17587,7 @@
         <v>225</v>
       </c>
       <c r="U29" s="1">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V29" t="s">
         <v>309</v>
@@ -17919,10 +17919,10 @@
         <v>220</v>
       </c>
       <c r="G30">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H30">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I30" t="s">
         <v>138</v>
@@ -17958,7 +17958,7 @@
         <v>144</v>
       </c>
       <c r="U30" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V30" t="s">
         <v>344</v>
@@ -18293,10 +18293,10 @@
         <v>220</v>
       </c>
       <c r="G31">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H31">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I31" t="s">
         <v>196</v>
@@ -18332,7 +18332,7 @@
         <v>144</v>
       </c>
       <c r="U31" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V31" t="s">
         <v>344</v>
@@ -18667,10 +18667,10 @@
         <v>220</v>
       </c>
       <c r="G32">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H32">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I32" t="s">
         <v>199</v>
@@ -18706,7 +18706,7 @@
         <v>144</v>
       </c>
       <c r="U32" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V32" t="s">
         <v>344</v>
@@ -19041,10 +19041,10 @@
         <v>220</v>
       </c>
       <c r="G33">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H33">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I33" t="s">
         <v>202</v>
@@ -19080,7 +19080,7 @@
         <v>144</v>
       </c>
       <c r="U33" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V33" t="s">
         <v>344</v>
@@ -19415,10 +19415,10 @@
         <v>220</v>
       </c>
       <c r="G34">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H34">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I34" t="s">
         <v>205</v>
@@ -19454,7 +19454,7 @@
         <v>144</v>
       </c>
       <c r="U34" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V34" t="s">
         <v>344</v>
@@ -19789,10 +19789,10 @@
         <v>220</v>
       </c>
       <c r="G35">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H35">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I35" t="s">
         <v>208</v>
@@ -19831,7 +19831,7 @@
         <v>144</v>
       </c>
       <c r="U35" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V35" t="s">
         <v>344</v>
@@ -20166,10 +20166,10 @@
         <v>220</v>
       </c>
       <c r="G36">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H36">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I36" t="s">
         <v>212</v>
@@ -20205,7 +20205,7 @@
         <v>144</v>
       </c>
       <c r="U36" s="1">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V36" t="s">
         <v>344</v>
@@ -20540,10 +20540,10 @@
         <v>220</v>
       </c>
       <c r="G37">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H37">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I37" t="s">
         <v>138</v>
@@ -20579,7 +20579,7 @@
         <v>144</v>
       </c>
       <c r="U37" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V37" t="s">
         <v>378</v>
@@ -20905,10 +20905,10 @@
         <v>220</v>
       </c>
       <c r="G38">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H38">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I38" t="s">
         <v>196</v>
@@ -20944,7 +20944,7 @@
         <v>144</v>
       </c>
       <c r="U38" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V38" t="s">
         <v>378</v>
@@ -21270,10 +21270,10 @@
         <v>220</v>
       </c>
       <c r="G39">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H39">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I39" t="s">
         <v>199</v>
@@ -21309,7 +21309,7 @@
         <v>144</v>
       </c>
       <c r="U39" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V39" t="s">
         <v>378</v>
@@ -21635,10 +21635,10 @@
         <v>220</v>
       </c>
       <c r="G40">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H40">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I40" t="s">
         <v>202</v>
@@ -21674,7 +21674,7 @@
         <v>144</v>
       </c>
       <c r="U40" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V40" t="s">
         <v>378</v>
@@ -22000,10 +22000,10 @@
         <v>220</v>
       </c>
       <c r="G41">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H41">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I41" t="s">
         <v>205</v>
@@ -22039,7 +22039,7 @@
         <v>144</v>
       </c>
       <c r="U41" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V41" t="s">
         <v>378</v>
@@ -22365,10 +22365,10 @@
         <v>220</v>
       </c>
       <c r="G42">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H42">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I42" t="s">
         <v>208</v>
@@ -22407,7 +22407,7 @@
         <v>144</v>
       </c>
       <c r="U42" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V42" t="s">
         <v>378</v>
@@ -22733,10 +22733,10 @@
         <v>220</v>
       </c>
       <c r="G43">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H43">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I43" t="s">
         <v>212</v>
@@ -22772,7 +22772,7 @@
         <v>144</v>
       </c>
       <c r="U43" s="1">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V43" t="s">
         <v>378</v>
@@ -23098,10 +23098,10 @@
         <v>413</v>
       </c>
       <c r="G44">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H44">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I44" t="s">
         <v>138</v>
@@ -23137,7 +23137,7 @@
         <v>225</v>
       </c>
       <c r="U44" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V44" t="s">
         <v>417</v>
@@ -23457,10 +23457,10 @@
         <v>413</v>
       </c>
       <c r="G45">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H45">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I45" t="s">
         <v>196</v>
@@ -23496,7 +23496,7 @@
         <v>225</v>
       </c>
       <c r="U45" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V45" t="s">
         <v>417</v>
@@ -23816,10 +23816,10 @@
         <v>413</v>
       </c>
       <c r="G46">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H46">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I46" t="s">
         <v>199</v>
@@ -23855,7 +23855,7 @@
         <v>225</v>
       </c>
       <c r="U46" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V46" t="s">
         <v>417</v>
@@ -24175,10 +24175,10 @@
         <v>413</v>
       </c>
       <c r="G47">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H47">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I47" t="s">
         <v>202</v>
@@ -24214,7 +24214,7 @@
         <v>225</v>
       </c>
       <c r="U47" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V47" t="s">
         <v>417</v>
@@ -24534,10 +24534,10 @@
         <v>413</v>
       </c>
       <c r="G48">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H48">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I48" t="s">
         <v>205</v>
@@ -24573,7 +24573,7 @@
         <v>225</v>
       </c>
       <c r="U48" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V48" t="s">
         <v>417</v>
@@ -24893,10 +24893,10 @@
         <v>413</v>
       </c>
       <c r="G49">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H49">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I49" t="s">
         <v>208</v>
@@ -24935,7 +24935,7 @@
         <v>225</v>
       </c>
       <c r="U49" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V49" t="s">
         <v>417</v>
@@ -25255,10 +25255,10 @@
         <v>413</v>
       </c>
       <c r="G50">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H50">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I50" t="s">
         <v>212</v>
@@ -25294,7 +25294,7 @@
         <v>225</v>
       </c>
       <c r="U50" s="1">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V50" t="s">
         <v>417</v>
@@ -25614,10 +25614,10 @@
         <v>449</v>
       </c>
       <c r="G51">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H51">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I51" t="s">
         <v>138</v>
@@ -25653,7 +25653,7 @@
         <v>144</v>
       </c>
       <c r="U51" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V51" t="s">
         <v>451</v>
@@ -25988,10 +25988,10 @@
         <v>449</v>
       </c>
       <c r="G52">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H52">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I52" t="s">
         <v>196</v>
@@ -26027,7 +26027,7 @@
         <v>144</v>
       </c>
       <c r="U52" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V52" t="s">
         <v>451</v>
@@ -26362,10 +26362,10 @@
         <v>449</v>
       </c>
       <c r="G53">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H53">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I53" t="s">
         <v>199</v>
@@ -26401,7 +26401,7 @@
         <v>144</v>
       </c>
       <c r="U53" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V53" t="s">
         <v>451</v>
@@ -26736,10 +26736,10 @@
         <v>449</v>
       </c>
       <c r="G54">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H54">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I54" t="s">
         <v>202</v>
@@ -26775,7 +26775,7 @@
         <v>144</v>
       </c>
       <c r="U54" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V54" t="s">
         <v>451</v>
@@ -27110,10 +27110,10 @@
         <v>449</v>
       </c>
       <c r="G55">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H55">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I55" t="s">
         <v>205</v>
@@ -27149,7 +27149,7 @@
         <v>144</v>
       </c>
       <c r="U55" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V55" t="s">
         <v>451</v>
@@ -27484,10 +27484,10 @@
         <v>449</v>
       </c>
       <c r="G56">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H56">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I56" t="s">
         <v>208</v>
@@ -27526,7 +27526,7 @@
         <v>144</v>
       </c>
       <c r="U56" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V56" t="s">
         <v>451</v>
@@ -27861,10 +27861,10 @@
         <v>449</v>
       </c>
       <c r="G57">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H57">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I57" t="s">
         <v>212</v>
@@ -27900,7 +27900,7 @@
         <v>144</v>
       </c>
       <c r="U57" s="1">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V57" t="s">
         <v>451</v>
@@ -28235,10 +28235,10 @@
         <v>220</v>
       </c>
       <c r="G58">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H58">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I58" t="s">
         <v>138</v>
@@ -28274,7 +28274,7 @@
         <v>225</v>
       </c>
       <c r="U58" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V58" t="s">
         <v>486</v>
@@ -28603,10 +28603,10 @@
         <v>220</v>
       </c>
       <c r="G59">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H59">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I59" t="s">
         <v>196</v>
@@ -28642,7 +28642,7 @@
         <v>225</v>
       </c>
       <c r="U59" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V59" t="s">
         <v>486</v>
@@ -28971,10 +28971,10 @@
         <v>220</v>
       </c>
       <c r="G60">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H60">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I60" t="s">
         <v>199</v>
@@ -29010,7 +29010,7 @@
         <v>225</v>
       </c>
       <c r="U60" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V60" t="s">
         <v>486</v>
@@ -29339,10 +29339,10 @@
         <v>220</v>
       </c>
       <c r="G61">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H61">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I61" t="s">
         <v>202</v>
@@ -29378,7 +29378,7 @@
         <v>225</v>
       </c>
       <c r="U61" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V61" t="s">
         <v>486</v>
@@ -29707,10 +29707,10 @@
         <v>220</v>
       </c>
       <c r="G62">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H62">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I62" t="s">
         <v>205</v>
@@ -29746,7 +29746,7 @@
         <v>225</v>
       </c>
       <c r="U62" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V62" t="s">
         <v>486</v>
@@ -30075,10 +30075,10 @@
         <v>220</v>
       </c>
       <c r="G63">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H63">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I63" t="s">
         <v>208</v>
@@ -30117,7 +30117,7 @@
         <v>225</v>
       </c>
       <c r="U63" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V63" t="s">
         <v>486</v>
@@ -30446,10 +30446,10 @@
         <v>220</v>
       </c>
       <c r="G64">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H64">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I64" t="s">
         <v>212</v>
@@ -30485,7 +30485,7 @@
         <v>225</v>
       </c>
       <c r="U64" s="1">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V64" t="s">
         <v>486</v>
@@ -30814,10 +30814,10 @@
         <v>220</v>
       </c>
       <c r="G65">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H65">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I65" t="s">
         <v>138</v>
@@ -30853,7 +30853,7 @@
         <v>144</v>
       </c>
       <c r="U65" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V65" t="s">
         <v>519</v>
@@ -31176,10 +31176,10 @@
         <v>220</v>
       </c>
       <c r="G66">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H66">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I66" t="s">
         <v>196</v>
@@ -31215,7 +31215,7 @@
         <v>144</v>
       </c>
       <c r="U66" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V66" t="s">
         <v>519</v>
@@ -31538,10 +31538,10 @@
         <v>220</v>
       </c>
       <c r="G67">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H67">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I67" t="s">
         <v>199</v>
@@ -31577,7 +31577,7 @@
         <v>144</v>
       </c>
       <c r="U67" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V67" t="s">
         <v>519</v>
@@ -31900,10 +31900,10 @@
         <v>220</v>
       </c>
       <c r="G68">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H68">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I68" t="s">
         <v>202</v>
@@ -31939,7 +31939,7 @@
         <v>144</v>
       </c>
       <c r="U68" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V68" t="s">
         <v>519</v>
@@ -32262,10 +32262,10 @@
         <v>220</v>
       </c>
       <c r="G69">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H69">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I69" t="s">
         <v>205</v>
@@ -32301,7 +32301,7 @@
         <v>144</v>
       </c>
       <c r="U69" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V69" t="s">
         <v>519</v>
@@ -32624,10 +32624,10 @@
         <v>220</v>
       </c>
       <c r="G70">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H70">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I70" t="s">
         <v>208</v>
@@ -32666,7 +32666,7 @@
         <v>144</v>
       </c>
       <c r="U70" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V70" t="s">
         <v>519</v>
@@ -32989,10 +32989,10 @@
         <v>220</v>
       </c>
       <c r="G71">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H71">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I71" t="s">
         <v>212</v>
@@ -33028,7 +33028,7 @@
         <v>144</v>
       </c>
       <c r="U71" s="1">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V71" t="s">
         <v>519</v>
@@ -33351,10 +33351,10 @@
         <v>413</v>
       </c>
       <c r="G72">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H72">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I72" t="s">
         <v>138</v>
@@ -33390,7 +33390,7 @@
         <v>225</v>
       </c>
       <c r="U72" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V72" t="s">
         <v>549</v>
@@ -33713,10 +33713,10 @@
         <v>413</v>
       </c>
       <c r="G73">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H73">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I73" t="s">
         <v>196</v>
@@ -33752,7 +33752,7 @@
         <v>225</v>
       </c>
       <c r="U73" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V73" t="s">
         <v>549</v>
@@ -34075,10 +34075,10 @@
         <v>413</v>
       </c>
       <c r="G74">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H74">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I74" t="s">
         <v>199</v>
@@ -34114,7 +34114,7 @@
         <v>225</v>
       </c>
       <c r="U74" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V74" t="s">
         <v>549</v>
@@ -34437,10 +34437,10 @@
         <v>413</v>
       </c>
       <c r="G75">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H75">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I75" t="s">
         <v>202</v>
@@ -34476,7 +34476,7 @@
         <v>225</v>
       </c>
       <c r="U75" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V75" t="s">
         <v>549</v>
@@ -34799,10 +34799,10 @@
         <v>413</v>
       </c>
       <c r="G76">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H76">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I76" t="s">
         <v>205</v>
@@ -34838,7 +34838,7 @@
         <v>225</v>
       </c>
       <c r="U76" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V76" t="s">
         <v>549</v>
@@ -35161,10 +35161,10 @@
         <v>413</v>
       </c>
       <c r="G77">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H77">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I77" t="s">
         <v>208</v>
@@ -35203,7 +35203,7 @@
         <v>225</v>
       </c>
       <c r="U77" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V77" t="s">
         <v>549</v>
@@ -35526,10 +35526,10 @@
         <v>413</v>
       </c>
       <c r="G78">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H78">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I78" t="s">
         <v>212</v>
@@ -35565,7 +35565,7 @@
         <v>225</v>
       </c>
       <c r="U78" s="1">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V78" t="s">
         <v>549</v>
@@ -35888,10 +35888,10 @@
         <v>577</v>
       </c>
       <c r="G79">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H79">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I79" t="s">
         <v>138</v>
@@ -35927,7 +35927,7 @@
         <v>144</v>
       </c>
       <c r="U79" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V79" t="s">
         <v>579</v>
@@ -36259,10 +36259,10 @@
         <v>577</v>
       </c>
       <c r="G80">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H80">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I80" t="s">
         <v>196</v>
@@ -36298,7 +36298,7 @@
         <v>144</v>
       </c>
       <c r="U80" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V80" t="s">
         <v>579</v>
@@ -36630,10 +36630,10 @@
         <v>577</v>
       </c>
       <c r="G81">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H81">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I81" t="s">
         <v>199</v>
@@ -36669,7 +36669,7 @@
         <v>144</v>
       </c>
       <c r="U81" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V81" t="s">
         <v>579</v>
@@ -37001,10 +37001,10 @@
         <v>577</v>
       </c>
       <c r="G82">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H82">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I82" t="s">
         <v>202</v>
@@ -37040,7 +37040,7 @@
         <v>144</v>
       </c>
       <c r="U82" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V82" t="s">
         <v>579</v>
@@ -37372,10 +37372,10 @@
         <v>577</v>
       </c>
       <c r="G83">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H83">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I83" t="s">
         <v>205</v>
@@ -37411,7 +37411,7 @@
         <v>144</v>
       </c>
       <c r="U83" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V83" t="s">
         <v>579</v>
@@ -37743,10 +37743,10 @@
         <v>577</v>
       </c>
       <c r="G84">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H84">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I84" t="s">
         <v>208</v>
@@ -37785,7 +37785,7 @@
         <v>144</v>
       </c>
       <c r="U84" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V84" t="s">
         <v>579</v>
@@ -38117,10 +38117,10 @@
         <v>577</v>
       </c>
       <c r="G85">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H85">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I85" t="s">
         <v>212</v>
@@ -38156,7 +38156,7 @@
         <v>144</v>
       </c>
       <c r="U85" s="1">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V85" t="s">
         <v>579</v>
